--- a/lessons/qr/excels/remarks_required.xlsx
+++ b/lessons/qr/excels/remarks_required.xlsx
@@ -172,7 +172,7 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-column (12:27:17.320), -mapContainer (12:50:07.768), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +cplumn (00:00:00), +  (00:00:00), +mapmarker (00:00:00)</t>
+        <t>-column (12:27:17.320) ~0.83, -mapContainer (12:50:07.768) ~0.50, -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +cplumn (00:00:00), +  (00:00:00), +mapmarker (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
@@ -212,12 +212,12 @@
     </comment>
     <comment ref="M14" authorId="0" shapeId="0">
       <text>
-        <t>-123456 (12:24:02.680), -marker (12:35:44.425), -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&gt; (12:53:08.192), -&lt; (12:59:27.700), -button (12:59:28.610), -id (12:59:29.226), -= (12:59:29.495), -" (12:59:30.073), -" (12:59:30.083), -btn (12:59:30.502), -onclick (12:59:42.303), -= (12:59:42.561), -" (12:59:43.422), -" (12:59:43.432), -toggleScanner (12:59:48.978), -( (12:59:49.262), -) (12:59:49.819), -&gt; (12:59:50.485), -&lt; (13:00:19.793), -/ (13:00:19.803), -button (13:00:19.863), -&gt; (13:00:19.873), -SCAN (13:00:21.378), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:17.454), -&lt; (13:07:17.983), -/ (13:07:17.993), -div (13:07:18.023), -&gt; (13:07:18.033), +654321 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +market (00:00:00)</t>
+        <t>-123456 (12:24:02.680) ~0.00, -marker (12:35:44.425) ~0.83, -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&gt; (12:53:08.192), -&lt; (12:59:27.700), -button (12:59:28.610), -id (12:59:29.226), -= (12:59:29.495), -" (12:59:30.073), -" (12:59:30.083), -btn (12:59:30.502), -onclick (12:59:42.303), -= (12:59:42.561), -" (12:59:43.422), -" (12:59:43.432), -toggleScanner (12:59:48.978), -( (12:59:49.262), -) (12:59:49.819), -&gt; (12:59:50.485), -&lt; (13:00:19.793), -/ (13:00:19.803), -button (13:00:19.863), -&gt; (13:00:19.873), -SCAN (13:00:21.378), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:17.454), -&lt; (13:07:17.983), -/ (13:07:17.993), -div (13:07:18.023), -&gt; (13:07:18.033), +654321 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +market (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q14" authorId="0" shapeId="0">
       <text>
-        <t>-facingMode (13:12:37.968), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -toggleScanner (13:20:36.733), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), +mapcontainer (00:00:00), +mapcontainer (00:00:00), +facingmode (00:00:00), +togglescanner (00:00:00)</t>
+        <t>-facingMode (13:12:37.968) ~0.90, -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -toggleScanner (13:20:36.733) ~0.92, -mapContainer (13:23:54.427) ~0.92, -mapContainer (13:24:12.088) ~0.92, +mapcontainer (00:00:00), +mapcontainer (00:00:00), +facingmode (00:00:00), +togglescanner (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D19" authorId="0" shapeId="0">
@@ -242,7 +242,7 @@
     </comment>
     <comment ref="M19" authorId="0" shapeId="0">
       <text>
-        <t>-id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -btn (12:59:30.502), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), +Btn (00:00:00)</t>
+        <t>-id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -btn (12:59:30.502) ~0.67, -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), +Btn (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O19" authorId="0" shapeId="0">
@@ -252,7 +252,7 @@
     </comment>
     <comment ref="Q19" authorId="0" shapeId="0">
       <text>
-        <t>-camera (13:10:05.606), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), +camere (00:00:00), +console (00:00:00), +. (00:00:00)</t>
+        <t>-camera (13:10:05.606) ~0.83, -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277) ~0.57, +camere (00:00:00), +console (00:00:00), +. (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D21" authorId="0" shapeId="0">
@@ -282,7 +282,7 @@
     </comment>
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
-        <t>-marker (12:56:29.330), -marker (12:57:07.602), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
+        <t>-marker (12:56:29.330) ~0.42, -marker (12:57:07.602) ~0.42, +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H24" authorId="0" shapeId="0">
@@ -322,12 +322,12 @@
     </comment>
     <comment ref="M25" authorId="0" shapeId="0">
       <text>
-        <t>-id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -mapContainer (12:49:01.909), -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&gt; (12:53:08.192), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +mapcontainer (00:00:00), += (00:00:00)</t>
+        <t>-id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -mapContainer (12:49:01.909) ~0.92, -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&gt; (12:53:08.192), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +mapcontainer (00:00:00), += (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>-mapContainer (12:50:07.768), +mapcontainer (00:00:00)</t>
+        <t>-mapContainer (12:50:07.768) ~0.92, +mapcontainer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -342,7 +342,7 @@
     </comment>
     <comment ref="M30" authorId="0" shapeId="0">
       <text>
-        <t>-qrcode (13:05:55.667), +sqrcode (00:00:00)</t>
+        <t>-qrcode (13:05:55.667) ~0.86, +sqrcode (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D31" authorId="0" shapeId="0">
@@ -372,7 +372,7 @@
     </comment>
     <comment ref="O31" authorId="0" shapeId="0">
       <text>
-        <t>-camera (13:08:26.947), +camer (00:00:00)</t>
+        <t>-camera (13:08:26.947) ~0.83, +camer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D36" authorId="0" shapeId="0">
@@ -397,12 +397,12 @@
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -: (13:05:50.571), +. (00:00:00)</t>
+        <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -: (13:05:50.571) ~0.00, +. (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q36" authorId="0" shapeId="0">
       <text>
-        <t>-startScanner (13:12:06.965), -showMarkerAt (13:20:05.930), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), +startsScanner (00:00:00), +showMarketAt (00:00:00)</t>
+        <t>-startScanner (13:12:06.965) ~0.92, -showMarkerAt (13:20:05.930) ~0.92, -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), +startsScanner (00:00:00), +showMarketAt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D41" authorId="0" shapeId="0">
@@ -427,17 +427,17 @@
     </comment>
     <comment ref="M41" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (12:19:34.294), -&lt; (12:19:35.624), -&lt; (12:21:30.346), -marker (12:35:44.425), -mapContainer (12:49:01.909), -&gt; (12:49:01.929), -script (12:52:45.286), -script (12:53:08.182), -script (13:05:47.673), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +map (00:00:00), +Container (00:00:00), +market (00:00:00), +srcipt (00:00:00), +sript (00:00:00), +srcipt (00:00:00), +sript (00:00:00)</t>
+        <t>-&lt; (12:19:34.294) ~0.00, -&lt; (12:19:35.624) ~0.00, -&lt; (12:21:30.346) ~0.00, -marker (12:35:44.425) ~0.83, -mapContainer (12:49:01.909), -&gt; (12:49:01.929), -script (12:52:45.286) ~0.67, -script (12:53:08.182) ~0.83, -script (13:05:47.673) ~0.67, -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081) ~0.83, +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +map (00:00:00), +Container (00:00:00), +market (00:00:00), +srcipt (00:00:00), +sript (00:00:00), +srcipt (00:00:00), +sript (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O41" authorId="0" shapeId="0">
       <text>
-        <t>-items (12:27:20.468), -} (12:27:40.523), -marker (12:36:09.957), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +item (00:00:00), +  (00:00:00), +market (00:00:00), +  (00:00:00)</t>
+        <t>-items (12:27:20.468) ~0.80, -} (12:27:40.523), -marker (12:36:09.957) ~0.83, -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +item (00:00:00), +  (00:00:00), +market (00:00:00), +  (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q41" authorId="0" shapeId="0">
       <text>
-        <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -} (13:02:27.642), -innerText (13:02:29.574), -CANCEL (13:02:31.086), -else (13:02:35.145), -{ (13:02:35.627), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -reader (13:09:44.738), -startScanner (13:11:29.686), -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -} (13:12:17.001), -function (13:14:37.982), -( (13:14:38.459), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +readerv (00:00:00), +startscanner8 (00:00:00), +innertext (00:00:00), +scan (00:00:00)</t>
+        <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -} (13:02:27.642), -innerText (13:02:29.574) ~0.89, -CANCEL (13:02:31.086) ~0.00, -else (13:02:35.145), -{ (13:02:35.627), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -reader (13:09:44.738) ~0.86, -startScanner (13:11:29.686) ~0.85, -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -} (13:12:17.001), -function (13:14:37.982), -( (13:14:38.459), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +readerv (00:00:00), +startscanner8 (00:00:00), +innertext (00:00:00), +scan (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D42" authorId="0" shapeId="0">
@@ -462,17 +462,17 @@
     </comment>
     <comment ref="M42" authorId="0" shapeId="0">
       <text>
-        <t>-script (12:52:45.286), +srcipt (00:00:00)</t>
+        <t>-script (12:52:45.286) ~0.67, +srcipt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-Arial (12:27:44.328), -marker (12:36:09.957), -border (12:38:55.775), +Artial (00:00:00), +market (00:00:00), +Border (00:00:00)</t>
+        <t>-Arial (12:27:44.328) ~0.83, -marker (12:36:09.957) ~0.83, -border (12:38:55.775) ~0.83, +Artial (00:00:00), +market (00:00:00), +Border (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q42" authorId="0" shapeId="0">
       <text>
-        <t>-showMarkerAt (13:20:05.930), +showMarketAt (00:00:00)</t>
+        <t>-showMarkerAt (13:20:05.930) ~0.92, +showMarketAt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E45" authorId="0" shapeId="0">
@@ -502,7 +502,7 @@
     </comment>
     <comment ref="Q45" authorId="0" shapeId="0">
       <text>
-        <t>-environment (13:12:42.232), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), +mapContainner (00:00:00), +mapContainner (00:00:00), +envitonment (00:00:00)</t>
+        <t>-environment (13:12:42.232) ~0.91, -mapContainer (13:23:54.427) ~0.92, -mapContainer (13:24:12.088) ~0.92, +mapContainner (00:00:00), +mapContainner (00:00:00), +envitonment (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D46" authorId="0" shapeId="0">
@@ -537,7 +537,7 @@
     </comment>
     <comment ref="Q46" authorId="0" shapeId="0">
       <text>
-        <t>-marker (12:56:29.330), -marker (12:57:07.602), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), +( (00:00:00), +) (00:00:00), +BigInt (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEl (00:00:00), +" (00:00:00), +; (00:00:00), +Marker (00:00:00), +Marker (00:00:00)</t>
+        <t>-marker (12:56:29.330) ~0.83, -marker (12:57:07.602) ~0.83, -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), +( (00:00:00), +) (00:00:00), +BigInt (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEl (00:00:00), +" (00:00:00), +; (00:00:00), +Marker (00:00:00), +Marker (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D48" authorId="0" shapeId="0">
@@ -562,7 +562,7 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-! (12:19:34.144), -viewport (12:19:34.954), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -/ (12:19:35.634), -title (12:19:35.684), -&gt; (12:19:35.694), -/ (12:21:30.356), -stylesheet (12:23:47.522), -href (12:23:59.034), -toggleScanner (12:59:48.978), -&gt; (13:06:51.091), +veiwport (00:00:00), +sytlesheet (00:00:00), +herf (00:00:00), +togglescanner (00:00:00)</t>
+        <t>-! (12:19:34.144), -viewport (12:19:34.954) ~0.75, -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -/ (12:19:35.634), -title (12:19:35.684), -&gt; (12:19:35.694), -/ (12:21:30.356), -stylesheet (12:23:47.522) ~0.80, -href (12:23:59.034) ~0.50, -toggleScanner (12:59:48.978) ~0.92, -&gt; (13:06:51.091) ~0.00, +veiwport (00:00:00), +sytlesheet (00:00:00), +herf (00:00:00), +togglescanner (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
@@ -572,7 +572,7 @@
     </comment>
     <comment ref="Q48" authorId="0" shapeId="0">
       <text>
-        <t>-scannerOn (13:00:41.475), -start (13:12:21.297), -environment (13:12:42.232), -showMarkerAt (13:20:05.930), +scannerON (00:00:00), +strat (00:00:00), +enviroment (00:00:00), +showMarketAt (00:00:00), +? (00:00:00)</t>
+        <t>-scannerOn (13:00:41.475) ~0.89, -start (13:12:21.297) ~0.60, -environment (13:12:42.232) ~0.91, -showMarkerAt (13:20:05.930) ~0.92, +scannerON (00:00:00), +strat (00:00:00), +enviroment (00:00:00), +showMarketAt (00:00:00), +? (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -592,7 +592,7 @@
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:19:34.954), -png (12:30:36.357), +viewpoint (00:00:00), +PNG (00:00:00)</t>
+        <t>-viewport (12:19:34.954) ~0.78, -png (12:30:36.357) ~0.00, +viewpoint (00:00:00), +PNG (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O50" authorId="0" shapeId="0">
@@ -602,7 +602,7 @@
     </comment>
     <comment ref="Q50" authorId="0" shapeId="0">
       <text>
-        <t>-= (12:57:18.822), -, (13:13:22.080), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +; (00:00:00), +- (00:00:00)</t>
+        <t>-= (12:57:18.822) ~0.00, -, (13:13:22.080) ~0.00, -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +; (00:00:00), +- (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E51" authorId="0" shapeId="0">
@@ -662,7 +662,7 @@
     </comment>
     <comment ref="Q59" authorId="0" shapeId="0">
       <text>
-        <t>-startScanner (13:11:29.686), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), +startcanner (00:00:00), +} (00:00:00)</t>
+        <t>-startScanner (13:11:29.686) ~0.92, -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), +startcanner (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D61" authorId="0" shapeId="0">
@@ -692,17 +692,17 @@
     </comment>
     <comment ref="O61" authorId="0" shapeId="0">
       <text>
-        <t>-mapContainer (12:50:07.768), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +mapcontainer (00:00:00)</t>
+        <t>-mapContainer (12:50:07.768) ~0.92, -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +mapcontainer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q61" authorId="0" shapeId="0">
       <text>
-        <t>-showMarkerAt (12:56:12.525), -btn (13:02:28.137), -innerText (13:02:29.574), -{ (13:02:35.627), -} (13:02:36.228), -btn (13:02:36.869), -innerText (13:02:38.115), -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -reader (13:12:18.420), -facingMode (13:12:37.968), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -, (13:20:08.279), -place (13:20:09.533), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +BigInt (00:00:00), +innertext (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +ReadableStream (00:00:00), +Facingmode (00:00:00), +) (00:00:00), +showMarkeAT (00:00:00)</t>
+        <t>-showMarkerAt (12:56:12.525) ~0.83, -btn (13:02:28.137) ~0.17, -innerText (13:02:29.574) ~0.89, -{ (13:02:35.627), -} (13:02:36.228), -btn (13:02:36.869) ~0.17, -innerText (13:02:38.115) ~0.89, -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -reader (13:12:18.420) ~0.36, -facingMode (13:12:37.968) ~0.80, -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -, (13:20:08.279), -place (13:20:09.533), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +BigInt (00:00:00), +innertext (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +ReadableStream (00:00:00), +Facingmode (00:00:00), +) (00:00:00), +showMarkeAT (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">
@@ -722,7 +722,7 @@
     </comment>
     <comment ref="Q62" authorId="0" shapeId="0">
       <text>
-        <t>-stopScanner (13:15:09.792), +stopSCanner (00:00:00)</t>
+        <t>-stopScanner (13:15:09.792) ~0.91, +stopSCanner (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D68" authorId="0" shapeId="0">
@@ -747,12 +747,12 @@
     </comment>
     <comment ref="M68" authorId="0" shapeId="0">
       <text>
-        <t>-mapContainer (12:49:01.909), -https (13:05:50.422), -: (13:05:50.571), -html5 (13:05:54.075), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), +mapcontainer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +http (00:00:00), +; (00:00:00), +html15 (00:00:00)</t>
+        <t>-mapContainer (12:49:01.909) ~0.92, -https (13:05:50.422) ~0.80, -: (13:05:50.571) ~0.00, -html5 (13:05:54.075) ~0.83, -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), +mapcontainer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +http (00:00:00), +; (00:00:00), +html15 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q68" authorId="0" shapeId="0">
       <text>
-        <t>-marker (12:56:29.330), -marker (12:57:07.602), -btn (13:02:28.137), -innerText (13:02:29.574), -btn (13:02:36.869), -innerText (13:02:38.115), -startScanner (13:12:06.965), -stopScanner (13:15:09.792), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), -block (13:24:16.075), +mapcantainer (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +mapcontainer (00:00:00), +black (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +startscanner (00:00:00), +stopscanner (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00), +} (00:00:00)</t>
+        <t>-marker (12:56:29.330) ~0.42, -marker (12:57:07.602) ~0.42, -btn (13:02:28.137) ~0.17, -innerText (13:02:29.574) ~0.89, -btn (13:02:36.869) ~0.17, -innerText (13:02:38.115) ~0.89, -startScanner (13:12:06.965) ~0.92, -stopScanner (13:15:09.792) ~0.91, -mapContainer (13:23:54.427) ~0.83, -mapContainer (13:24:12.088) ~0.92, -block (13:24:16.075) ~0.80, +mapcantainer (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +mapcontainer (00:00:00), +black (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +startscanner (00:00:00), +stopscanner (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D70" authorId="0" shapeId="0">
@@ -777,7 +777,7 @@
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-! (12:19:34.144), -- (12:19:35.194), -width (12:19:35.244), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -&gt; (12:19:35.454), -html5 (13:05:54.075), +html15 (00:00:00)</t>
+        <t>-! (12:19:34.144), -- (12:19:35.194), -width (12:19:35.244), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -&gt; (12:19:35.454), -html5 (13:05:54.075) ~0.83, +html15 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
@@ -787,7 +787,7 @@
     </comment>
     <comment ref="Q70" authorId="0" shapeId="0">
       <text>
-        <t>-startScanner (13:11:29.686), -startScanner (13:12:06.965), +StartScanner (00:00:00), +startsScanner (00:00:00)</t>
+        <t>-startScanner (13:11:29.686) ~0.92, -startScanner (13:12:06.965) ~0.92, +StartScanner (00:00:00), +startsScanner (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D71" authorId="0" shapeId="0">
@@ -817,12 +817,12 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -toggleScanner (12:59:48.978), -html5 (13:05:54.075), +toggScanner (00:00:00), +html15 (00:00:00)</t>
+        <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -toggleScanner (12:59:48.978) ~0.85, -html5 (13:05:54.075) ~0.83, +toggScanner (00:00:00), +html15 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q72" authorId="0" shapeId="0">
       <text>
-        <t>-left (12:57:18.355), -btn (13:02:28.137), -btn (13:02:36.869), -Html5Qrcode (13:09:48.612), -showMarkerAt (13:20:05.930), +HTML5QRcode (00:00:00), +bnt (00:00:00), +bnt (00:00:00), +showmarkerAt (00:00:00), +top (00:00:00)</t>
+        <t>-left (12:57:18.355) ~0.00, -btn (13:02:28.137) ~0.33, -btn (13:02:36.869) ~0.33, -Html5Qrcode (13:09:48.612) ~0.64, -showMarkerAt (13:20:05.930) ~0.92, +HTML5QRcode (00:00:00), +bnt (00:00:00), +bnt (00:00:00), +showmarkerAt (00:00:00), +top (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D73" authorId="0" shapeId="0">
@@ -852,7 +852,7 @@
     </comment>
     <comment ref="Q73" authorId="0" shapeId="0">
       <text>
-        <t>-Html5Qrcode (13:09:48.612), +HTML5Qrcode (00:00:00)</t>
+        <t>-Html5Qrcode (13:09:48.612) ~0.73, +HTML5Qrcode (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D78" authorId="0" shapeId="0">
@@ -872,7 +872,7 @@
     </comment>
     <comment ref="M78" authorId="0" shapeId="0">
       <text>
-        <t>-toggleScanner (12:59:48.978), +toogleScanner (00:00:00)</t>
+        <t>-toggleScanner (12:59:48.978) ~0.92, +toogleScanner (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D79" authorId="0" shapeId="0">
@@ -897,7 +897,7 @@
     </comment>
     <comment ref="Q79" authorId="0" shapeId="0">
       <text>
-        <t>-error (13:14:54.485), +log (00:00:00)</t>
+        <t>-error (13:14:54.485) ~0.20, +log (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H81" authorId="0" shapeId="0">
@@ -937,7 +937,7 @@
     </comment>
     <comment ref="Q83" authorId="0" shapeId="0">
       <text>
-        <t>-Html5Qrcode (13:09:48.612), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +Html5QRcode (00:00:00)</t>
+        <t>-Html5Qrcode (13:09:48.612) ~0.91, -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +Html5QRcode (00:00:00)</t>
       </text>
     </comment>
   </commentList>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-column (12:27:17.320), -mapContainer (12:50:07.768), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +cplumn (00:00:00), +  (00:00:00), +mapmarker (00:00:00)</t>
+          <t>-column (12:27:17.320) ~0.83, -mapContainer (12:50:07.768) ~0.50, -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +cplumn (00:00:00), +  (00:00:00), +mapmarker (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>-123456 (12:24:02.680), -marker (12:35:44.425), -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&gt; (12:53:08.192), -&lt; (12:59:27.700), -button (12:59:28.610), -id (12:59:29.226), -= (12:59:29.495), -" (12:59:30.073), -" (12:59:30.083), -btn (12:59:30.502), -onclick (12:59:42.303), -= (12:59:42.561), -" (12:59:43.422), -" (12:59:43.432), -toggleScanner (12:59:48.978), -( (12:59:49.262), -) (12:59:49.819), -&gt; (12:59:50.485), -&lt; (13:00:19.793), -/ (13:00:19.803), -button (13:00:19.863), -&gt; (13:00:19.873), -SCAN (13:00:21.378), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:17.454), -&lt; (13:07:17.983), -/ (13:07:17.993), -div (13:07:18.023), -&gt; (13:07:18.033), +654321 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +market (00:00:00)</t>
+          <t>-123456 (12:24:02.680) ~0.00, -marker (12:35:44.425) ~0.83, -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&gt; (12:53:08.192), -&lt; (12:59:27.700), -button (12:59:28.610), -id (12:59:29.226), -= (12:59:29.495), -" (12:59:30.073), -" (12:59:30.083), -btn (12:59:30.502), -onclick (12:59:42.303), -= (12:59:42.561), -" (12:59:43.422), -" (12:59:43.432), -toggleScanner (12:59:48.978), -( (12:59:49.262), -) (12:59:49.819), -&gt; (12:59:50.485), -&lt; (13:00:19.793), -/ (13:00:19.803), -button (13:00:19.863), -&gt; (13:00:19.873), -SCAN (13:00:21.378), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:17.454), -&lt; (13:07:17.983), -/ (13:07:17.993), -div (13:07:18.023), -&gt; (13:07:18.033), +654321 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +market (00:00:00)</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>-facingMode (13:12:37.968), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -toggleScanner (13:20:36.733), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), +mapcontainer (00:00:00), +mapcontainer (00:00:00), +facingmode (00:00:00), +togglescanner (00:00:00)</t>
+          <t>-facingMode (13:12:37.968) ~0.90, -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -toggleScanner (13:20:36.733) ~0.92, -mapContainer (13:23:54.427) ~0.92, -mapContainer (13:24:12.088) ~0.92, +mapcontainer (00:00:00), +mapcontainer (00:00:00), +facingmode (00:00:00), +togglescanner (00:00:00)</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -btn (12:59:30.502), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), +Btn (00:00:00)</t>
+          <t>-id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -btn (12:59:30.502) ~0.67, -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), +Btn (00:00:00)</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>-camera (13:10:05.606), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), +camere (00:00:00), +console (00:00:00), +. (00:00:00)</t>
+          <t>-camera (13:10:05.606) ~0.83, -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277) ~0.57, +camere (00:00:00), +console (00:00:00), +. (00:00:00)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>-marker (12:56:29.330), -marker (12:57:07.602), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
+          <t>-marker (12:56:29.330) ~0.42, -marker (12:57:07.602) ~0.42, +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -mapContainer (12:49:01.909), -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&gt; (12:53:08.192), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +mapcontainer (00:00:00), += (00:00:00)</t>
+          <t>-id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -mapContainer (12:49:01.909) ~0.92, -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&gt; (12:53:08.192), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +mapcontainer (00:00:00), += (00:00:00)</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-mapContainer (12:50:07.768), +mapcontainer (00:00:00)</t>
+          <t>-mapContainer (12:50:07.768) ~0.92, +mapcontainer (00:00:00)</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-qrcode (13:05:55.667), +sqrcode (00:00:00)</t>
+          <t>-qrcode (13:05:55.667) ~0.86, +sqrcode (00:00:00)</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-camera (13:08:26.947), +camer (00:00:00)</t>
+          <t>-camera (13:08:26.947) ~0.83, +camer (00:00:00)</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -: (13:05:50.571), +. (00:00:00)</t>
+          <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -: (13:05:50.571) ~0.00, +. (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-startScanner (13:12:06.965), -showMarkerAt (13:20:05.930), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), +startsScanner (00:00:00), +showMarketAt (00:00:00)</t>
+          <t>-startScanner (13:12:06.965) ~0.92, -showMarkerAt (13:20:05.930) ~0.92, -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), +startsScanner (00:00:00), +showMarketAt (00:00:00)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>-&lt; (12:19:34.294), -&lt; (12:19:35.624), -&lt; (12:21:30.346), -marker (12:35:44.425), -mapContainer (12:49:01.909), -&gt; (12:49:01.929), -script (12:52:45.286), -script (12:53:08.182), -script (13:05:47.673), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +map (00:00:00), +Container (00:00:00), +market (00:00:00), +srcipt (00:00:00), +sript (00:00:00), +srcipt (00:00:00), +sript (00:00:00)</t>
+          <t>-&lt; (12:19:34.294) ~0.00, -&lt; (12:19:35.624) ~0.00, -&lt; (12:21:30.346) ~0.00, -marker (12:35:44.425) ~0.83, -mapContainer (12:49:01.909), -&gt; (12:49:01.929), -script (12:52:45.286) ~0.67, -script (12:53:08.182) ~0.83, -script (13:05:47.673) ~0.67, -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081) ~0.83, +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +map (00:00:00), +Container (00:00:00), +market (00:00:00), +srcipt (00:00:00), +sript (00:00:00), +srcipt (00:00:00), +sript (00:00:00)</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-items (12:27:20.468), -} (12:27:40.523), -marker (12:36:09.957), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +item (00:00:00), +  (00:00:00), +market (00:00:00), +  (00:00:00)</t>
+          <t>-items (12:27:20.468) ~0.80, -} (12:27:40.523), -marker (12:36:09.957) ~0.83, -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +item (00:00:00), +  (00:00:00), +market (00:00:00), +  (00:00:00)</t>
         </is>
       </c>
       <c r="Q41" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -} (13:02:27.642), -innerText (13:02:29.574), -CANCEL (13:02:31.086), -else (13:02:35.145), -{ (13:02:35.627), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -reader (13:09:44.738), -startScanner (13:11:29.686), -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -} (13:12:17.001), -function (13:14:37.982), -( (13:14:38.459), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +readerv (00:00:00), +startscanner8 (00:00:00), +innertext (00:00:00), +scan (00:00:00)</t>
+          <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -} (13:02:27.642), -innerText (13:02:29.574) ~0.89, -CANCEL (13:02:31.086) ~0.00, -else (13:02:35.145), -{ (13:02:35.627), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -reader (13:09:44.738) ~0.86, -startScanner (13:11:29.686) ~0.85, -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -} (13:12:17.001), -function (13:14:37.982), -( (13:14:38.459), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +readerv (00:00:00), +startscanner8 (00:00:00), +innertext (00:00:00), +scan (00:00:00)</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-script (12:52:45.286), +srcipt (00:00:00)</t>
+          <t>-script (12:52:45.286) ~0.67, +srcipt (00:00:00)</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-Arial (12:27:44.328), -marker (12:36:09.957), -border (12:38:55.775), +Artial (00:00:00), +market (00:00:00), +Border (00:00:00)</t>
+          <t>-Arial (12:27:44.328) ~0.83, -marker (12:36:09.957) ~0.83, -border (12:38:55.775) ~0.83, +Artial (00:00:00), +market (00:00:00), +Border (00:00:00)</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>-showMarkerAt (13:20:05.930), +showMarketAt (00:00:00)</t>
+          <t>-showMarkerAt (13:20:05.930) ~0.92, +showMarketAt (00:00:00)</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>-environment (13:12:42.232), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), +mapContainner (00:00:00), +mapContainner (00:00:00), +envitonment (00:00:00)</t>
+          <t>-environment (13:12:42.232) ~0.91, -mapContainer (13:23:54.427) ~0.92, -mapContainer (13:24:12.088) ~0.92, +mapContainner (00:00:00), +mapContainner (00:00:00), +envitonment (00:00:00)</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>-marker (12:56:29.330), -marker (12:57:07.602), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), +( (00:00:00), +) (00:00:00), +BigInt (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEl (00:00:00), +" (00:00:00), +; (00:00:00), +Marker (00:00:00), +Marker (00:00:00)</t>
+          <t>-marker (12:56:29.330) ~0.83, -marker (12:57:07.602) ~0.83, -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), +( (00:00:00), +) (00:00:00), +BigInt (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEl (00:00:00), +" (00:00:00), +; (00:00:00), +Marker (00:00:00), +Marker (00:00:00)</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-! (12:19:34.144), -viewport (12:19:34.954), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -/ (12:19:35.634), -title (12:19:35.684), -&gt; (12:19:35.694), -/ (12:21:30.356), -stylesheet (12:23:47.522), -href (12:23:59.034), -toggleScanner (12:59:48.978), -&gt; (13:06:51.091), +veiwport (00:00:00), +sytlesheet (00:00:00), +herf (00:00:00), +togglescanner (00:00:00)</t>
+          <t>-! (12:19:34.144), -viewport (12:19:34.954) ~0.75, -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -/ (12:19:35.634), -title (12:19:35.684), -&gt; (12:19:35.694), -/ (12:21:30.356), -stylesheet (12:23:47.522) ~0.80, -href (12:23:59.034) ~0.50, -toggleScanner (12:59:48.978) ~0.92, -&gt; (13:06:51.091) ~0.00, +veiwport (00:00:00), +sytlesheet (00:00:00), +herf (00:00:00), +togglescanner (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>-scannerOn (13:00:41.475), -start (13:12:21.297), -environment (13:12:42.232), -showMarkerAt (13:20:05.930), +scannerON (00:00:00), +strat (00:00:00), +enviroment (00:00:00), +showMarketAt (00:00:00), +? (00:00:00)</t>
+          <t>-scannerOn (13:00:41.475) ~0.89, -start (13:12:21.297) ~0.60, -environment (13:12:42.232) ~0.91, -showMarkerAt (13:20:05.930) ~0.92, +scannerON (00:00:00), +strat (00:00:00), +enviroment (00:00:00), +showMarketAt (00:00:00), +? (00:00:00)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-viewport (12:19:34.954), -png (12:30:36.357), +viewpoint (00:00:00), +PNG (00:00:00)</t>
+          <t>-viewport (12:19:34.954) ~0.78, -png (12:30:36.357) ~0.00, +viewpoint (00:00:00), +PNG (00:00:00)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>-= (12:57:18.822), -, (13:13:22.080), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +; (00:00:00), +- (00:00:00)</t>
+          <t>-= (12:57:18.822) ~0.00, -, (13:13:22.080) ~0.00, -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +; (00:00:00), +- (00:00:00)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>-startScanner (13:11:29.686), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), +startcanner (00:00:00), +} (00:00:00)</t>
+          <t>-startScanner (13:11:29.686) ~0.92, -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), +startcanner (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>-mapContainer (12:50:07.768), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +mapcontainer (00:00:00)</t>
+          <t>-mapContainer (12:50:07.768) ~0.92, -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +mapcontainer (00:00:00)</t>
         </is>
       </c>
       <c r="Q61" t="n">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>-showMarkerAt (12:56:12.525), -btn (13:02:28.137), -innerText (13:02:29.574), -{ (13:02:35.627), -} (13:02:36.228), -btn (13:02:36.869), -innerText (13:02:38.115), -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -reader (13:12:18.420), -facingMode (13:12:37.968), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -, (13:20:08.279), -place (13:20:09.533), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +BigInt (00:00:00), +innertext (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +ReadableStream (00:00:00), +Facingmode (00:00:00), +) (00:00:00), +showMarkeAT (00:00:00)</t>
+          <t>-showMarkerAt (12:56:12.525) ~0.83, -btn (13:02:28.137) ~0.17, -innerText (13:02:29.574) ~0.89, -{ (13:02:35.627), -} (13:02:36.228), -btn (13:02:36.869) ~0.17, -innerText (13:02:38.115) ~0.89, -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -reader (13:12:18.420) ~0.36, -facingMode (13:12:37.968) ~0.80, -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -, (13:20:08.279), -place (13:20:09.533), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +BigInt (00:00:00), +innertext (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +ReadableStream (00:00:00), +Facingmode (00:00:00), +) (00:00:00), +showMarkeAT (00:00:00)</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>-stopScanner (13:15:09.792), +stopSCanner (00:00:00)</t>
+          <t>-stopScanner (13:15:09.792) ~0.91, +stopSCanner (00:00:00)</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>-mapContainer (12:49:01.909), -https (13:05:50.422), -: (13:05:50.571), -html5 (13:05:54.075), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), +mapcontainer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +http (00:00:00), +; (00:00:00), +html15 (00:00:00)</t>
+          <t>-mapContainer (12:49:01.909) ~0.92, -https (13:05:50.422) ~0.80, -: (13:05:50.571) ~0.00, -html5 (13:05:54.075) ~0.83, -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), +mapcontainer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +http (00:00:00), +; (00:00:00), +html15 (00:00:00)</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>-marker (12:56:29.330), -marker (12:57:07.602), -btn (13:02:28.137), -innerText (13:02:29.574), -btn (13:02:36.869), -innerText (13:02:38.115), -startScanner (13:12:06.965), -stopScanner (13:15:09.792), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), -block (13:24:16.075), +mapcantainer (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +mapcontainer (00:00:00), +black (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +startscanner (00:00:00), +stopscanner (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00), +} (00:00:00)</t>
+          <t>-marker (12:56:29.330) ~0.42, -marker (12:57:07.602) ~0.42, -btn (13:02:28.137) ~0.17, -innerText (13:02:29.574) ~0.89, -btn (13:02:36.869) ~0.17, -innerText (13:02:38.115) ~0.89, -startScanner (13:12:06.965) ~0.92, -stopScanner (13:15:09.792) ~0.91, -mapContainer (13:23:54.427) ~0.83, -mapContainer (13:24:12.088) ~0.92, -block (13:24:16.075) ~0.80, +mapcantainer (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +mapcontainer (00:00:00), +black (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +startscanner (00:00:00), +stopscanner (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-! (12:19:34.144), -- (12:19:35.194), -width (12:19:35.244), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -&gt; (12:19:35.454), -html5 (13:05:54.075), +html15 (00:00:00)</t>
+          <t>-! (12:19:34.144), -- (12:19:35.194), -width (12:19:35.244), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -&gt; (12:19:35.454), -html5 (13:05:54.075) ~0.83, +html15 (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>-startScanner (13:11:29.686), -startScanner (13:12:06.965), +StartScanner (00:00:00), +startsScanner (00:00:00)</t>
+          <t>-startScanner (13:11:29.686) ~0.92, -startScanner (13:12:06.965) ~0.92, +StartScanner (00:00:00), +startsScanner (00:00:00)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -toggleScanner (12:59:48.978), -html5 (13:05:54.075), +toggScanner (00:00:00), +html15 (00:00:00)</t>
+          <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -toggleScanner (12:59:48.978) ~0.85, -html5 (13:05:54.075) ~0.83, +toggScanner (00:00:00), +html15 (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>-left (12:57:18.355), -btn (13:02:28.137), -btn (13:02:36.869), -Html5Qrcode (13:09:48.612), -showMarkerAt (13:20:05.930), +HTML5QRcode (00:00:00), +bnt (00:00:00), +bnt (00:00:00), +showmarkerAt (00:00:00), +top (00:00:00)</t>
+          <t>-left (12:57:18.355) ~0.00, -btn (13:02:28.137) ~0.33, -btn (13:02:36.869) ~0.33, -Html5Qrcode (13:09:48.612) ~0.64, -showMarkerAt (13:20:05.930) ~0.92, +HTML5QRcode (00:00:00), +bnt (00:00:00), +bnt (00:00:00), +showmarkerAt (00:00:00), +top (00:00:00)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>-Html5Qrcode (13:09:48.612), +HTML5Qrcode (00:00:00)</t>
+          <t>-Html5Qrcode (13:09:48.612) ~0.73, +HTML5Qrcode (00:00:00)</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>-toggleScanner (12:59:48.978), +toogleScanner (00:00:00)</t>
+          <t>-toggleScanner (12:59:48.978) ~0.92, +toogleScanner (00:00:00)</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>-error (13:14:54.485), +log (00:00:00)</t>
+          <t>-error (13:14:54.485) ~0.20, +log (00:00:00)</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>-Html5Qrcode (13:09:48.612), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +Html5QRcode (00:00:00)</t>
+          <t>-Html5Qrcode (13:09:48.612) ~0.91, -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +Html5QRcode (00:00:00)</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
